--- a/testprocess/0-templet/sequoiadb-test-process.xlsx
+++ b/testprocess/0-templet/sequoiadb-test-process.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="7"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="project-info" sheetId="1" r:id="rId1"/>
@@ -108,14 +108,6 @@
   </si>
   <si>
     <t>该表格用于填写测试项目基本信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>项目背景：……
-项目需求：……
-测试目标：……
-测试方式：……
-实现方式：……</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -568,6 +560,123 @@
   </si>
   <si>
     <t>此处可以写一些其它信息。例如测试环境配置、注意事项等等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目背景</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">：……
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目需求</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">：……
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>测试目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">：……
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>测试方式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">：……
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实现方式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：……</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1382,20 +1491,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1517,9 +1614,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1538,136 +1632,136 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1676,6 +1770,39 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="7" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1685,38 +1812,20 @@
     <xf numFmtId="14" fontId="7" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1805,10 +1914,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.10750984251968505"/>
-          <c:y val="0.13851639218788742"/>
-          <c:w val="0.538357529527559"/>
-          <c:h val="0.3768597929792859"/>
+          <c:x val="0.10750984251968507"/>
+          <c:y val="0.13851639218788747"/>
+          <c:w val="0.53835752952755889"/>
+          <c:h val="0.37685979297928601"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -1853,24 +1962,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="86289024"/>
-        <c:axId val="86315392"/>
+        <c:axId val="175204224"/>
+        <c:axId val="175205760"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86289024"/>
+        <c:axId val="175204224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="86315392"/>
+        <c:crossAx val="175205760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86315392"/>
+        <c:axId val="175205760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1878,7 +1987,7 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="86289024"/>
+        <c:crossAx val="175204224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1890,7 +1999,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -2220,23 +2329,23 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="99.375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="99.375" style="7" customWidth="1"/>
     <col min="3" max="3" width="66.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="67"/>
+      <c r="B1" s="62"/>
     </row>
     <row r="2" spans="1:3" ht="14.25" thickBot="1"/>
     <row r="3" spans="1:3" ht="25.5">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="127"/>
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2244,8 +2353,8 @@
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="128"/>
+      <c r="C4" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2253,8 +2362,8 @@
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="128"/>
+      <c r="C5" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2262,8 +2371,8 @@
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="129"/>
+      <c r="C6" s="8" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2271,8 +2380,8 @@
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="129"/>
+      <c r="C7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2280,116 +2389,116 @@
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="130"/>
+      <c r="C8" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="40.5" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="64" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="63" t="s">
+      <c r="B9" s="126" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="59" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="69"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="63"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="59"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="69"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="63"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="59"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="69"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="63"/>
+      <c r="A12" s="64"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="59"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="69"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="63"/>
+      <c r="A13" s="64"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="59"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="69"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="63"/>
+      <c r="A14" s="64"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="59"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="69"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="63"/>
+      <c r="A15" s="64"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="59"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="69"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="63"/>
+      <c r="A16" s="64"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="59"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="69"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="63"/>
+      <c r="A17" s="64"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="59"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="69"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="63"/>
+      <c r="A18" s="64"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="59"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="69"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="63"/>
+      <c r="A19" s="64"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="59"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="69"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="63"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="59"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="69"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="63"/>
+      <c r="A21" s="64"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="59"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="69"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="63"/>
+      <c r="A22" s="64"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="59"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="69"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="63"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="59"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="69"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="63"/>
+      <c r="A24" s="64"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="59"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="69"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="63"/>
+      <c r="A25" s="64"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="59"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="69"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="63"/>
+      <c r="A26" s="64"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="59"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="69"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="63"/>
+      <c r="A27" s="64"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="59"/>
     </row>
     <row r="28" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A28" s="70"/>
-      <c r="B28" s="66"/>
-      <c r="C28" s="63"/>
+      <c r="A28" s="65"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2409,419 +2518,442 @@
   <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="10.375" style="23" customWidth="1"/>
-    <col min="2" max="3" width="13.625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="23" customWidth="1"/>
-    <col min="5" max="5" width="13.75" style="23" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="23" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="23" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="23"/>
+    <col min="1" max="1" width="10.375" style="19" customWidth="1"/>
+    <col min="2" max="3" width="13.625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="19" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="19" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="19" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="19" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="19" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+    </row>
+    <row r="3" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A3" s="72" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="86" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="70"/>
+      <c r="M4" s="93"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="74"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="108"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="74"/>
+      <c r="B6" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="108"/>
+    </row>
+    <row r="7" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A7" s="75"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="108"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="87" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="82"/>
+      <c r="M8" s="108"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="74"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
+      <c r="M9" s="108"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="74"/>
+      <c r="B10" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="82"/>
+      <c r="L10" s="82"/>
+      <c r="M10" s="108"/>
+    </row>
+    <row r="11" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A11" s="75"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="109"/>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A17" s="71" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+    </row>
+    <row r="18" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A18" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-    </row>
-    <row r="3" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A3" s="106" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="107" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="71" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="71"/>
-      <c r="M4" s="72"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="108"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="74"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="108"/>
-      <c r="B6" s="114" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="111" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="74"/>
-    </row>
-    <row r="7" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A7" s="109"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="74"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="112" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="77" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="73"/>
-      <c r="L8" s="73"/>
-      <c r="M8" s="74"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="108"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="73"/>
-      <c r="M9" s="74"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="108"/>
-      <c r="B10" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="73"/>
-      <c r="L10" s="73"/>
-      <c r="M10" s="74"/>
-    </row>
-    <row r="11" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A11" s="109"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="75"/>
-      <c r="M11" s="76"/>
-    </row>
-    <row r="17" spans="1:13" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A17" s="105" t="s">
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="70"/>
+      <c r="M18" s="93"/>
+    </row>
+    <row r="19" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A19" s="68"/>
+      <c r="B19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="94"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="78"/>
+    </row>
+    <row r="20" spans="1:13" ht="18" customHeight="1">
+      <c r="A20" s="68"/>
+      <c r="B20" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="97"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="107"/>
+    </row>
+    <row r="21" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A21" s="68"/>
+      <c r="B21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="94"/>
+      <c r="D21" s="95"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="78"/>
+    </row>
+    <row r="22" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A22" s="69"/>
+      <c r="B22" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="99"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="80"/>
+      <c r="M22" s="81"/>
+    </row>
+    <row r="27" spans="1:13" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A27" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="105"/>
-      <c r="C17" s="105"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
-    </row>
-    <row r="18" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A18" s="102" t="s">
+      <c r="B27" s="92"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="92"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="89" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="32"/>
+    </row>
+    <row r="29" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A29" s="90"/>
+      <c r="B29" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="D29" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="90"/>
+      <c r="B30" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="71" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71" t="s">
-        <v>33</v>
-      </c>
-      <c r="L18" s="71"/>
-      <c r="M18" s="72"/>
-    </row>
-    <row r="19" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A19" s="103"/>
-      <c r="B19" s="33" t="s">
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="90"/>
+      <c r="B31" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="83"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="91"/>
-      <c r="M19" s="99"/>
-    </row>
-    <row r="20" spans="1:13" ht="18" customHeight="1">
-      <c r="A20" s="103"/>
-      <c r="B20" s="34" t="s">
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="90"/>
+      <c r="B32" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="14.25" thickBot="1">
+      <c r="A33" s="91"/>
+      <c r="B33" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="85" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="86"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="95"/>
-      <c r="K20" s="93"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="100"/>
-    </row>
-    <row r="21" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A21" s="103"/>
-      <c r="B21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="83"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="91"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="91"/>
-      <c r="M21" s="99"/>
-    </row>
-    <row r="22" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A22" s="104"/>
-      <c r="B22" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="88"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="97"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="97"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="96"/>
-      <c r="L22" s="97"/>
-      <c r="M22" s="110"/>
-    </row>
-    <row r="27" spans="1:13" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A27" s="82" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="82"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="82"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="82"/>
-      <c r="H27" s="82"/>
-      <c r="I27" s="82"/>
-      <c r="J27" s="82"/>
-      <c r="K27" s="82"/>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="36"/>
-    </row>
-    <row r="29" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A29" s="80"/>
-      <c r="B29" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="80"/>
-      <c r="B30" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="80"/>
-      <c r="B31" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="37" t="s">
+      <c r="C33" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="80"/>
-      <c r="B32" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="14.25" thickBot="1">
-      <c r="A33" s="81"/>
-      <c r="B33" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40" t="s">
-        <v>27</v>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="K4:M5"/>
+    <mergeCell ref="K6:M7"/>
+    <mergeCell ref="K8:M9"/>
+    <mergeCell ref="K10:M11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F4:J5"/>
+    <mergeCell ref="F6:J7"/>
+    <mergeCell ref="F8:J9"/>
+    <mergeCell ref="F10:J11"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="C18:E18"/>
@@ -2838,29 +2970,6 @@
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K4:M5"/>
-    <mergeCell ref="K6:M7"/>
-    <mergeCell ref="K8:M9"/>
-    <mergeCell ref="K10:M11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F4:J5"/>
-    <mergeCell ref="F6:J7"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="F10:J11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2874,9 +2983,9 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.875" customWidth="1"/>
-    <col min="2" max="2" width="79.75" style="18" customWidth="1"/>
+    <col min="2" max="2" width="79.75" style="14" customWidth="1"/>
     <col min="3" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="47.125" style="18" customWidth="1"/>
+    <col min="5" max="5" width="47.125" style="14" customWidth="1"/>
     <col min="6" max="6" width="19.875" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
   </cols>
@@ -2885,61 +2994,61 @@
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" thickBot="1">
-      <c r="A2" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="41"/>
-    </row>
-    <row r="3" spans="1:7" s="14" customFormat="1" ht="19.5" thickBot="1">
-      <c r="A3" s="15" t="s">
+      <c r="A2" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="110"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" s="10" customFormat="1" ht="19.5" thickBot="1">
+      <c r="A3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="19" t="s">
+      <c r="D3" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
-      <c r="F4" s="101" t="s">
+      <c r="F4" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="101"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7"/>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="21"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2962,574 +3071,574 @@
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="29" customFormat="1">
-      <c r="A1" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="28" t="s">
+    <row r="1" spans="1:41" s="25" customFormat="1">
+      <c r="A1" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="30"/>
-      <c r="AL1" s="30"/>
-      <c r="AM1" s="30"/>
-      <c r="AN1" s="30"/>
-      <c r="AO1" s="30"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="26"/>
+      <c r="AI1" s="26"/>
+      <c r="AJ1" s="26"/>
+      <c r="AK1" s="26"/>
+      <c r="AL1" s="26"/>
+      <c r="AM1" s="26"/>
+      <c r="AN1" s="26"/>
+      <c r="AO1" s="26"/>
     </row>
     <row r="2" spans="1:41">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="3" spans="1:41">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
     </row>
     <row r="4" spans="1:41">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="1:41">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
     </row>
     <row r="6" spans="1:41">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
     </row>
     <row r="7" spans="1:41">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
     </row>
     <row r="8" spans="1:41">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
     </row>
     <row r="9" spans="1:41">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
     </row>
     <row r="10" spans="1:41">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
     </row>
     <row r="11" spans="1:41">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
     </row>
     <row r="12" spans="1:41">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
     </row>
     <row r="13" spans="1:41">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
     </row>
     <row r="14" spans="1:41">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
     </row>
     <row r="15" spans="1:41">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
     </row>
     <row r="16" spans="1:41">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="26"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="26"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="26"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="26"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="26"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="26"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="26"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="26"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="26"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="26"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="26"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="26"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="26"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="26"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="26"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="26"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="26"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="26"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="26"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="26"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
+      <c r="A51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="26"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
+      <c r="A52" s="22"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="26"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="26"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="26"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="26"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="26"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="26"/>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="26"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="26"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="26"/>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="26"/>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="26"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="22"/>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="26"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
+      <c r="A64" s="22"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="22"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="26"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
+      <c r="A65" s="22"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="26"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
+      <c r="A66" s="22"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="26"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
+      <c r="A67" s="22"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="26"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="26"/>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
+      <c r="A69" s="22"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="26"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="26"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="26"/>
+      <c r="A71" s="22"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="22"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="26"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26"/>
+      <c r="A72" s="22"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="22"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="26"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
+      <c r="A73" s="22"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="22"/>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="26"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
+      <c r="A74" s="22"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="22"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="26"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
+      <c r="A75" s="22"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="22"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="26"/>
-      <c r="B76" s="26"/>
-      <c r="C76" s="26"/>
+      <c r="A76" s="22"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="26"/>
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
+      <c r="A77" s="22"/>
+      <c r="B77" s="22"/>
+      <c r="C77" s="22"/>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="26"/>
-      <c r="B78" s="26"/>
-      <c r="C78" s="26"/>
+      <c r="A78" s="22"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="26"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
+      <c r="A79" s="22"/>
+      <c r="B79" s="22"/>
+      <c r="C79" s="22"/>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="26"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
+      <c r="A80" s="22"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="26"/>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
+      <c r="A81" s="22"/>
+      <c r="B81" s="22"/>
+      <c r="C81" s="22"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="26"/>
-      <c r="B82" s="26"/>
-      <c r="C82" s="26"/>
+      <c r="A82" s="22"/>
+      <c r="B82" s="22"/>
+      <c r="C82" s="22"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="26"/>
-      <c r="B83" s="26"/>
-      <c r="C83" s="26"/>
+      <c r="A83" s="22"/>
+      <c r="B83" s="22"/>
+      <c r="C83" s="22"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="26"/>
-      <c r="B84" s="26"/>
-      <c r="C84" s="26"/>
+      <c r="A84" s="22"/>
+      <c r="B84" s="22"/>
+      <c r="C84" s="22"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="26"/>
-      <c r="B85" s="26"/>
-      <c r="C85" s="26"/>
+      <c r="A85" s="22"/>
+      <c r="B85" s="22"/>
+      <c r="C85" s="22"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="26"/>
-      <c r="B86" s="26"/>
-      <c r="C86" s="26"/>
+      <c r="A86" s="22"/>
+      <c r="B86" s="22"/>
+      <c r="C86" s="22"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="26"/>
-      <c r="B87" s="26"/>
-      <c r="C87" s="26"/>
+      <c r="A87" s="22"/>
+      <c r="B87" s="22"/>
+      <c r="C87" s="22"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="26"/>
-      <c r="B88" s="26"/>
-      <c r="C88" s="26"/>
+      <c r="A88" s="22"/>
+      <c r="B88" s="22"/>
+      <c r="C88" s="22"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="26"/>
-      <c r="B89" s="26"/>
-      <c r="C89" s="26"/>
+      <c r="A89" s="22"/>
+      <c r="B89" s="22"/>
+      <c r="C89" s="22"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="26"/>
-      <c r="B90" s="26"/>
-      <c r="C90" s="26"/>
+      <c r="A90" s="22"/>
+      <c r="B90" s="22"/>
+      <c r="C90" s="22"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="26"/>
-      <c r="B91" s="26"/>
-      <c r="C91" s="26"/>
+      <c r="A91" s="22"/>
+      <c r="B91" s="22"/>
+      <c r="C91" s="22"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="26"/>
-      <c r="B92" s="26"/>
-      <c r="C92" s="26"/>
+      <c r="A92" s="22"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="22"/>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="26"/>
-      <c r="B93" s="26"/>
-      <c r="C93" s="26"/>
+      <c r="A93" s="22"/>
+      <c r="B93" s="22"/>
+      <c r="C93" s="22"/>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="26"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="26"/>
+      <c r="A94" s="22"/>
+      <c r="B94" s="22"/>
+      <c r="C94" s="22"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="26"/>
-      <c r="B95" s="26"/>
-      <c r="C95" s="26"/>
+      <c r="A95" s="22"/>
+      <c r="B95" s="22"/>
+      <c r="C95" s="22"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="26"/>
-      <c r="B96" s="26"/>
-      <c r="C96" s="26"/>
+      <c r="A96" s="22"/>
+      <c r="B96" s="22"/>
+      <c r="C96" s="22"/>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="26"/>
-      <c r="B97" s="26"/>
-      <c r="C97" s="26"/>
+      <c r="A97" s="22"/>
+      <c r="B97" s="22"/>
+      <c r="C97" s="22"/>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="26"/>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
+      <c r="A98" s="22"/>
+      <c r="B98" s="22"/>
+      <c r="C98" s="22"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="26"/>
-      <c r="B99" s="26"/>
-      <c r="C99" s="26"/>
+      <c r="A99" s="22"/>
+      <c r="B99" s="22"/>
+      <c r="C99" s="22"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="26"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="26"/>
+      <c r="A100" s="22"/>
+      <c r="B100" s="22"/>
+      <c r="C100" s="22"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="26"/>
-      <c r="B101" s="26"/>
-      <c r="C101" s="26"/>
+      <c r="A101" s="22"/>
+      <c r="B101" s="22"/>
+      <c r="C101" s="22"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="26"/>
-      <c r="B102" s="26"/>
-      <c r="C102" s="26"/>
+      <c r="A102" s="22"/>
+      <c r="B102" s="22"/>
+      <c r="C102" s="22"/>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="26"/>
-      <c r="B103" s="26"/>
-      <c r="C103" s="26"/>
+      <c r="A103" s="22"/>
+      <c r="B103" s="22"/>
+      <c r="C103" s="22"/>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="26"/>
-      <c r="B104" s="26"/>
-      <c r="C104" s="26"/>
+      <c r="A104" s="22"/>
+      <c r="B104" s="22"/>
+      <c r="C104" s="22"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="26"/>
-      <c r="B105" s="26"/>
-      <c r="C105" s="26"/>
+      <c r="A105" s="22"/>
+      <c r="B105" s="22"/>
+      <c r="C105" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3542,179 +3651,179 @@
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="43"/>
+    <col min="1" max="1" width="11.125" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A3" s="43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="68"/>
+      <c r="B5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="68"/>
+      <c r="B6" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="68"/>
+      <c r="B7" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A3" s="47" t="s">
+    <row r="8" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A8" s="69"/>
+      <c r="B8" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A16" s="43" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="14.25" thickBot="1">
+      <c r="A17" s="123" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="102" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="103"/>
-      <c r="B5" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="103"/>
-      <c r="B6" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="103"/>
-      <c r="B7" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A8" s="104"/>
-      <c r="B8" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="43" t="s">
+      <c r="B17" s="124"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="125"/>
+    </row>
+    <row r="18" spans="1:5" ht="13.5" customHeight="1">
+      <c r="A18" s="112" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A16" s="47" t="s">
+      <c r="B18" s="114" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="116"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="112"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="119"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="112"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="119"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="112"/>
+      <c r="B21" s="117"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="119"/>
+    </row>
+    <row r="22" spans="1:5" ht="14.25" thickBot="1">
+      <c r="A22" s="113"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="121"/>
+      <c r="D22" s="121"/>
+      <c r="E22" s="122"/>
+    </row>
+    <row r="23" spans="1:5" ht="14.25" thickBot="1">
+      <c r="A23" s="123" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="124"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="125"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="112" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="114" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="115"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="116"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="112"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="119"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="112"/>
+      <c r="B26" s="117"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="119"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="112"/>
+      <c r="B27" s="117"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="119"/>
+    </row>
+    <row r="28" spans="1:5" ht="14.25" thickBot="1">
+      <c r="A28" s="113"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="121"/>
+      <c r="D28" s="121"/>
+      <c r="E28" s="122"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="39" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="14.25" thickBot="1">
-      <c r="A17" s="117" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="118"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="119"/>
-    </row>
-    <row r="18" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A18" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="122" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="123"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="124"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="120"/>
-      <c r="B19" s="125"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="127"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="120"/>
-      <c r="B20" s="125"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="127"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="120"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="127"/>
-    </row>
-    <row r="22" spans="1:5" ht="14.25" thickBot="1">
-      <c r="A22" s="121"/>
-      <c r="B22" s="128"/>
-      <c r="C22" s="129"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="130"/>
-    </row>
-    <row r="23" spans="1:5" ht="14.25" thickBot="1">
-      <c r="A23" s="117" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="118"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="119"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="122" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="123"/>
-      <c r="D24" s="123"/>
-      <c r="E24" s="124"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="120"/>
-      <c r="B25" s="125"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="127"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="120"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="127"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="120"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="127"/>
-    </row>
-    <row r="28" spans="1:5" ht="14.25" thickBot="1">
-      <c r="A28" s="121"/>
-      <c r="B28" s="128"/>
-      <c r="C28" s="129"/>
-      <c r="D28" s="129"/>
-      <c r="E28" s="130"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="43" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3738,214 +3847,214 @@
   <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.875" style="43" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="43"/>
+    <col min="1" max="1" width="13.875" style="39" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
+      <c r="A1" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" thickBot="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="39" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="68"/>
+      <c r="B4" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="68"/>
+      <c r="B5" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="68"/>
+      <c r="B6" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.25" thickBot="1">
+      <c r="A7" s="69"/>
+      <c r="B7" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14.25" thickBot="1">
+      <c r="A9" s="39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="102" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="103"/>
-      <c r="B4" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="103"/>
-      <c r="B5" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="103"/>
-      <c r="B6" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.25" thickBot="1">
-      <c r="A7" s="104"/>
-      <c r="B7" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="14.25" thickBot="1">
-      <c r="A9" s="43" t="s">
+    <row r="10" spans="1:7">
+      <c r="A10" s="48" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="52" t="s">
+      <c r="B10" s="44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="48" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="53" t="s">
+      <c r="B11" s="45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="14.25" thickBot="1">
+      <c r="A12" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="39" t="s">
         <v>83</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="14.25" thickBot="1">
-      <c r="A12" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="43" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.25" thickBot="1"/>
     <row r="18" spans="1:7">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="53" t="s">
+      <c r="B19" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="57">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="53" t="s">
+      <c r="B20" s="53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="14.25" thickBot="1">
+      <c r="A22" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="57">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="14.25" thickBot="1">
-      <c r="A22" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="43" t="s">
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="39" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="50" t="s">
+    <row r="34" spans="1:7">
+      <c r="A34" s="39" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="39" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="39" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="43" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="43" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="43" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="43" t="s">
+      <c r="B39" s="47"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="39" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="43" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="43" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3964,130 +4073,130 @@
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="9" style="43"/>
+    <col min="1" max="16384" width="9" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="39" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="39" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="39" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="54"/>
+      <c r="B5" s="39" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="43" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="43" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="43" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="58"/>
-      <c r="B5" s="43" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="55"/>
+      <c r="B6" s="39" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="59"/>
-      <c r="B6" s="43" t="s">
-        <v>97</v>
-      </c>
-    </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="43" t="s">
-        <v>106</v>
+      <c r="A8" s="39" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="62" t="s">
-        <v>116</v>
+      <c r="A11" s="58" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="60" t="s">
-        <v>107</v>
+      <c r="A19" s="56" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="62" t="s">
-        <v>108</v>
+      <c r="A21" s="58" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="61" t="s">
-        <v>109</v>
+      <c r="A25" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4101,12 +4210,12 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="9" style="43"/>
+    <col min="1" max="16384" width="9" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="43" t="s">
-        <v>118</v>
+      <c r="A1" s="39" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
